--- a/results/models/summary_all_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
+++ b/results/models/summary_all_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
@@ -536,28 +536,28 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.059</v>
+        <v>0.846</v>
       </c>
       <c r="I2" t="n">
-        <v>32.8802</v>
+        <v>34.0089</v>
       </c>
       <c r="J2" t="n">
-        <v>31.746</v>
+        <v>32.3437</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7807</v>
+        <v>1.6651</v>
       </c>
       <c r="L2" t="n">
-        <v>31.746</v>
+        <v>32.3437</v>
       </c>
       <c r="M2" t="n">
         <v>0.9952</v>
       </c>
       <c r="N2" t="n">
-        <v>7.0246</v>
+        <v>7.1429</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1599</v>
+        <v>4.1558</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -599,28 +599,28 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.058</v>
+        <v>0.589</v>
       </c>
       <c r="I3" t="n">
-        <v>32.909</v>
+        <v>34.1212</v>
       </c>
       <c r="J3" t="n">
-        <v>31.746</v>
+        <v>32.3437</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8766</v>
+        <v>1.7775</v>
       </c>
       <c r="L3" t="n">
-        <v>31.746</v>
+        <v>32.3437</v>
       </c>
       <c r="M3" t="n">
         <v>0.9952</v>
       </c>
       <c r="N3" t="n">
-        <v>7.0246</v>
+        <v>7.1429</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1599</v>
+        <v>4.1558</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -662,28 +662,28 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.047</v>
+        <v>0.633</v>
       </c>
       <c r="I4" t="n">
-        <v>32.856</v>
+        <v>33.8481</v>
       </c>
       <c r="J4" t="n">
-        <v>31.7016</v>
+        <v>32.271</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8478</v>
+        <v>1.5771</v>
       </c>
       <c r="L4" t="n">
-        <v>31.7016</v>
+        <v>32.271</v>
       </c>
       <c r="M4" t="n">
         <v>0.9952</v>
       </c>
       <c r="N4" t="n">
-        <v>7.068</v>
+        <v>7.3572</v>
       </c>
       <c r="O4" t="n">
-        <v>4.155</v>
+        <v>4.1891</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.047</v>
+        <v>0.594</v>
       </c>
       <c r="I5" t="n">
-        <v>33.4449</v>
+        <v>34.6717</v>
       </c>
       <c r="J5" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8109</v>
+        <v>2.328</v>
       </c>
       <c r="L5" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="M5" t="n">
         <v>0.9952</v>
       </c>
       <c r="N5" t="n">
-        <v>7.068</v>
+        <v>7.1429</v>
       </c>
       <c r="O5" t="n">
-        <v>4.155</v>
+        <v>4.1558</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -788,28 +788,28 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.047</v>
+        <v>0.665</v>
       </c>
       <c r="I6" t="n">
-        <v>33.4025</v>
+        <v>34.6992</v>
       </c>
       <c r="J6" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6696</v>
+        <v>2.3555</v>
       </c>
       <c r="L6" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="M6" t="n">
         <v>0.9952</v>
       </c>
       <c r="N6" t="n">
-        <v>7.068</v>
+        <v>7.1429</v>
       </c>
       <c r="O6" t="n">
-        <v>4.155</v>
+        <v>4.1558</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -851,28 +851,28 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.047</v>
+        <v>0.584</v>
       </c>
       <c r="I7" t="n">
-        <v>33.4771</v>
+        <v>34.6245</v>
       </c>
       <c r="J7" t="n">
-        <v>31.7016</v>
+        <v>32.271</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9182</v>
+        <v>2.3535</v>
       </c>
       <c r="L7" t="n">
-        <v>31.7016</v>
+        <v>32.271</v>
       </c>
       <c r="M7" t="n">
         <v>0.9952</v>
       </c>
       <c r="N7" t="n">
-        <v>7.068</v>
+        <v>7.3572</v>
       </c>
       <c r="O7" t="n">
-        <v>4.155</v>
+        <v>4.1891</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -914,28 +914,28 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.044</v>
+        <v>0.627</v>
       </c>
       <c r="I8" t="n">
-        <v>33.1053</v>
+        <v>34.2363</v>
       </c>
       <c r="J8" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6789</v>
+        <v>1.8926</v>
       </c>
       <c r="L8" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="M8" t="n">
         <v>0.9952</v>
       </c>
       <c r="N8" t="n">
-        <v>7.068</v>
+        <v>7.1429</v>
       </c>
       <c r="O8" t="n">
-        <v>4.155</v>
+        <v>4.1558</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.044</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>33.0961</v>
+        <v>34.3915</v>
       </c>
       <c r="J9" t="n">
-        <v>31.7584</v>
+        <v>32.4005</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4591</v>
+        <v>1.991</v>
       </c>
       <c r="L9" t="n">
-        <v>31.7584</v>
+        <v>32.4005</v>
       </c>
       <c r="M9" t="n">
         <v>0.9952</v>
       </c>
       <c r="N9" t="n">
-        <v>7.121</v>
+        <v>7.1959</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1677</v>
+        <v>4.1685</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1040,28 +1040,28 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.043</v>
+        <v>0.608</v>
       </c>
       <c r="I10" t="n">
-        <v>33.3944</v>
+        <v>34.4742</v>
       </c>
       <c r="J10" t="n">
-        <v>31.7016</v>
+        <v>32.1492</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6427</v>
+        <v>2.325</v>
       </c>
       <c r="L10" t="n">
-        <v>31.7016</v>
+        <v>32.1492</v>
       </c>
       <c r="M10" t="n">
         <v>0.9952</v>
       </c>
       <c r="N10" t="n">
-        <v>7.068</v>
+        <v>7.5507</v>
       </c>
       <c r="O10" t="n">
-        <v>4.155</v>
+        <v>4.1617</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1103,28 +1103,28 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.042</v>
+        <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>33.4703</v>
+        <v>34.7358</v>
       </c>
       <c r="J11" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8955</v>
+        <v>2.3921</v>
       </c>
       <c r="L11" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="M11" t="n">
         <v>0.9952</v>
       </c>
       <c r="N11" t="n">
-        <v>7.068</v>
+        <v>7.1429</v>
       </c>
       <c r="O11" t="n">
-        <v>4.155</v>
+        <v>4.1558</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1166,28 +1166,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.043</v>
+        <v>0.616</v>
       </c>
       <c r="I12" t="n">
-        <v>33.4411</v>
+        <v>34.7722</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="K12" t="n">
-        <v>5.7983</v>
+        <v>2.4284</v>
       </c>
       <c r="L12" t="n">
-        <v>31.7016</v>
+        <v>32.3437</v>
       </c>
       <c r="M12" t="n">
         <v>0.9952</v>
       </c>
       <c r="N12" t="n">
-        <v>7.068</v>
+        <v>7.1429</v>
       </c>
       <c r="O12" t="n">
-        <v>4.155</v>
+        <v>4.1558</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.044</v>
+        <v>0.606</v>
       </c>
       <c r="I13" t="n">
-        <v>33.4663</v>
+        <v>34.6153</v>
       </c>
       <c r="J13" t="n">
-        <v>31.7016</v>
+        <v>32.271</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8821</v>
+        <v>2.3443</v>
       </c>
       <c r="L13" t="n">
-        <v>31.7016</v>
+        <v>32.271</v>
       </c>
       <c r="M13" t="n">
         <v>0.9952</v>
       </c>
       <c r="N13" t="n">
-        <v>7.068</v>
+        <v>7.3572</v>
       </c>
       <c r="O13" t="n">
-        <v>4.155</v>
+        <v>4.1891</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>

--- a/results/models/summary_all_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
+++ b/results/models/summary_all_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
@@ -536,28 +536,28 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.846</v>
+        <v>0.162</v>
       </c>
       <c r="I2" t="n">
-        <v>34.0089</v>
+        <v>32.8802</v>
       </c>
       <c r="J2" t="n">
-        <v>32.3437</v>
+        <v>31.746</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6651</v>
+        <v>1.1342</v>
       </c>
       <c r="L2" t="n">
-        <v>32.3437</v>
+        <v>31.746</v>
       </c>
       <c r="M2" t="n">
         <v>0.9952</v>
       </c>
       <c r="N2" t="n">
-        <v>7.1429</v>
+        <v>7.0246</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1558</v>
+        <v>4.1599</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -599,28 +599,28 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.589</v>
+        <v>0.136</v>
       </c>
       <c r="I3" t="n">
-        <v>34.1212</v>
+        <v>32.909</v>
       </c>
       <c r="J3" t="n">
-        <v>32.3437</v>
+        <v>31.746</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7775</v>
+        <v>1.163</v>
       </c>
       <c r="L3" t="n">
-        <v>32.3437</v>
+        <v>31.746</v>
       </c>
       <c r="M3" t="n">
         <v>0.9952</v>
       </c>
       <c r="N3" t="n">
-        <v>7.1429</v>
+        <v>7.0246</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1558</v>
+        <v>4.1599</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -662,28 +662,28 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.633</v>
+        <v>0.157</v>
       </c>
       <c r="I4" t="n">
-        <v>33.8481</v>
+        <v>32.856</v>
       </c>
       <c r="J4" t="n">
-        <v>32.271</v>
+        <v>31.7016</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5771</v>
+        <v>1.1543</v>
       </c>
       <c r="L4" t="n">
-        <v>32.271</v>
+        <v>31.7016</v>
       </c>
       <c r="M4" t="n">
         <v>0.9952</v>
       </c>
       <c r="N4" t="n">
-        <v>7.3572</v>
+        <v>7.068</v>
       </c>
       <c r="O4" t="n">
-        <v>4.1891</v>
+        <v>4.155</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.594</v>
+        <v>0.138</v>
       </c>
       <c r="I5" t="n">
-        <v>34.6717</v>
+        <v>33.4449</v>
       </c>
       <c r="J5" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="K5" t="n">
-        <v>2.328</v>
+        <v>1.7433</v>
       </c>
       <c r="L5" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="M5" t="n">
         <v>0.9952</v>
       </c>
       <c r="N5" t="n">
-        <v>7.1429</v>
+        <v>7.068</v>
       </c>
       <c r="O5" t="n">
-        <v>4.1558</v>
+        <v>4.155</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -788,28 +788,28 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.665</v>
+        <v>0.134</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6992</v>
+        <v>33.4025</v>
       </c>
       <c r="J6" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3555</v>
+        <v>1.7009</v>
       </c>
       <c r="L6" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="M6" t="n">
         <v>0.9952</v>
       </c>
       <c r="N6" t="n">
-        <v>7.1429</v>
+        <v>7.068</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1558</v>
+        <v>4.155</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -851,28 +851,28 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.584</v>
+        <v>0.138</v>
       </c>
       <c r="I7" t="n">
-        <v>34.6245</v>
+        <v>33.4771</v>
       </c>
       <c r="J7" t="n">
-        <v>32.271</v>
+        <v>31.7016</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3535</v>
+        <v>1.7755</v>
       </c>
       <c r="L7" t="n">
-        <v>32.271</v>
+        <v>31.7016</v>
       </c>
       <c r="M7" t="n">
         <v>0.9952</v>
       </c>
       <c r="N7" t="n">
-        <v>7.3572</v>
+        <v>7.068</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1891</v>
+        <v>4.155</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -914,28 +914,28 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.627</v>
+        <v>0.136</v>
       </c>
       <c r="I8" t="n">
-        <v>34.2363</v>
+        <v>33.1053</v>
       </c>
       <c r="J8" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8926</v>
+        <v>1.4037</v>
       </c>
       <c r="L8" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="M8" t="n">
         <v>0.9952</v>
       </c>
       <c r="N8" t="n">
-        <v>7.1429</v>
+        <v>7.068</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1558</v>
+        <v>4.155</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.162</v>
       </c>
       <c r="I9" t="n">
-        <v>34.3915</v>
+        <v>33.0961</v>
       </c>
       <c r="J9" t="n">
-        <v>32.4005</v>
+        <v>31.7584</v>
       </c>
       <c r="K9" t="n">
-        <v>1.991</v>
+        <v>1.3377</v>
       </c>
       <c r="L9" t="n">
-        <v>32.4005</v>
+        <v>31.7584</v>
       </c>
       <c r="M9" t="n">
         <v>0.9952</v>
       </c>
       <c r="N9" t="n">
-        <v>7.1959</v>
+        <v>7.121</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1685</v>
+        <v>4.1677</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1040,28 +1040,28 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.608</v>
+        <v>0.141</v>
       </c>
       <c r="I10" t="n">
-        <v>34.4742</v>
+        <v>33.3944</v>
       </c>
       <c r="J10" t="n">
-        <v>32.1492</v>
+        <v>31.7016</v>
       </c>
       <c r="K10" t="n">
-        <v>2.325</v>
+        <v>1.6928</v>
       </c>
       <c r="L10" t="n">
-        <v>32.1492</v>
+        <v>31.7016</v>
       </c>
       <c r="M10" t="n">
         <v>0.9952</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5507</v>
+        <v>7.068</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1617</v>
+        <v>4.155</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1103,28 +1103,28 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.6</v>
+        <v>0.184</v>
       </c>
       <c r="I11" t="n">
-        <v>34.7358</v>
+        <v>33.4703</v>
       </c>
       <c r="J11" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3921</v>
+        <v>1.7687</v>
       </c>
       <c r="L11" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="M11" t="n">
         <v>0.9952</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1429</v>
+        <v>7.068</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1558</v>
+        <v>4.155</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1166,28 +1166,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.616</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>34.7722</v>
+        <v>33.4411</v>
       </c>
       <c r="J12" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4284</v>
+        <v>1.7395</v>
       </c>
       <c r="L12" t="n">
-        <v>32.3437</v>
+        <v>31.7016</v>
       </c>
       <c r="M12" t="n">
         <v>0.9952</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1429</v>
+        <v>7.068</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1558</v>
+        <v>4.155</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.606</v>
+        <v>0.143</v>
       </c>
       <c r="I13" t="n">
-        <v>34.6153</v>
+        <v>33.4663</v>
       </c>
       <c r="J13" t="n">
-        <v>32.271</v>
+        <v>31.7016</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3443</v>
+        <v>1.7646</v>
       </c>
       <c r="L13" t="n">
-        <v>32.271</v>
+        <v>31.7016</v>
       </c>
       <c r="M13" t="n">
         <v>0.9952</v>
       </c>
       <c r="N13" t="n">
-        <v>7.3572</v>
+        <v>7.068</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1891</v>
+        <v>4.155</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
